--- a/models/sovereigns/Oman_Sovereign_Model.xlsx
+++ b/models/sovereigns/Oman_Sovereign_Model.xlsx
@@ -874,16 +874,34 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>7.5</v>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -891,16 +909,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>6.156</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1042,16 +1078,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>117.176</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Oman_Sovereign_Model.xlsx
+++ b/models/sovereigns/Oman_Sovereign_Model.xlsx
@@ -671,16 +671,34 @@
           <t>cpi_latest_yoy_pct</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="2" t="n">
+        <v>3.3771</v>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IMF CPI database</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IMF CPI database, all items, y/y % change, monthly (auto-filled; a run's sourced point replaces it unless older)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -703,19 +721,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NCSI</t>
+          <t>National Centre for Statistics and Information</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jun-25</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>non-hydrocarbon ~3.5%</t>
-        </is>
-      </c>
+          <t>30-Jun-25</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -750,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>end-2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -760,10 +774,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dec-25</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>31-Dec-25</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Central government debt; end-2025 approximate</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -789,7 +807,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -803,19 +821,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance</t>
+          <t>Ministry of Finance / IMF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dec-25</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>stated as ~0.6-0.7% surplus</t>
-        </is>
-      </c>
+          <t>30-Jun-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -875,7 +889,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -884,24 +898,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>Central Bank of Oman / IMF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+          <t>30-Jun-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -954,7 +964,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>end-2024</t>
+          <t>Dec-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -964,12 +974,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dec-24</t>
+          <t>31-Dec-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross foreign assets and gold, OMR 7.068bn</t>
+          <t>CBO gross foreign assets and gold (OMR 7.068bn); excludes OIA assets</t>
         </is>
       </c>
     </row>
@@ -1006,17 +1016,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>end-2024</t>
+          <t>Dec-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Central Bank of Oman</t>
+          <t>Central Bank of Oman (reported as over 5 months of merchandise imports)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dec-24</t>
+          <t>31-Dec-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1237,7 +1247,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27-Sep-24</t>
+          <t>27-Sep-24 (upgrade); affirmed Sep-26</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1358,11 @@
       </c>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>National Centre for Statistics and Information, 30-Jun-25</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1369,10 +1383,18 @@
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
+      <c r="C5" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>2.5</v>
+      </c>
       <c r="E5" s="2" t="n"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Central Bank of Oman / IMF, 30-Jun-26</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1385,14 +1407,14 @@
         <v>3.3</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>4.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ministry of Finance / IMF, Jun-26 (2026E from report view)</t>
+          <t>Ministry of Finance / IMF, 30-Jun-26 (2026E is an IMF projection)</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1448,7 @@
       <c r="E8" s="2" t="n"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ministry of Finance, Dec-25</t>
+          <t>Ministry of Finance, 31-Dec-25</t>
         </is>
       </c>
     </row>
@@ -1449,10 +1471,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
+      <c r="C10" s="2" t="n">
+        <v>18.38</v>
+      </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Central Bank of Oman, 31-Dec-24</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/models/sovereigns/Oman_Sovereign_Model.xlsx
+++ b/models/sovereigns/Oman_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/oman.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/oman.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Oman_Sovereign_Model.xlsx
+++ b/models/sovereigns/Oman_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-Jun-25</t>
+          <t>Jun-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -774,12 +774,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31-Dec-25</t>
+          <t>Dec-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Central government debt; end-2025 approximate</t>
+          <t>Central government debt</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -908,7 +908,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -964,22 +964,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Central Bank of Oman</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Dec-24</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Central Bank of Oman</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>31-Dec-24</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBO gross foreign assets and gold (OMR 7.068bn); excludes OIA assets</t>
+          <t>CBO gross foreign assets and gold (OMR 7.068bn)</t>
         </is>
       </c>
     </row>
@@ -1016,17 +1016,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Central Bank of Oman</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Dec-24</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Central Bank of Oman (reported as over 5 months of merchandise imports)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>31-Dec-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27-Sep-24 (upgrade); affirmed Sep-26</t>
+          <t>27-Sep-24</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1330,6 +1330,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>2026F</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
@@ -1344,7 +1349,8 @@
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1358,9 +1364,10 @@
       </c>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>National Centre for Statistics and Information, 30-Jun-25</t>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>National Centre for Statistics and Information, Jun-25</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1381,8 @@
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1390,9 +1398,10 @@
         <v>2.5</v>
       </c>
       <c r="E5" s="2" t="n"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Central Bank of Oman / IMF, 30-Jun-26</t>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Central Bank of Oman / IMF, Jun-26</t>
         </is>
       </c>
     </row>
@@ -1412,9 +1421,12 @@
       <c r="E6" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ministry of Finance / IMF, 30-Jun-26 (2026E is an IMF projection)</t>
+      <c r="F6" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ministry of Finance / IMF, Jun-26</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1440,8 @@
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1446,9 +1459,10 @@
         <v>34.7</v>
       </c>
       <c r="E8" s="2" t="n"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Ministry of Finance, 31-Dec-25</t>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ministry of Finance, Dec-25</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1476,8 @@
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1476,9 +1491,10 @@
       </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Central Bank of Oman, 31-Dec-24</t>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Central Bank of Oman, Dec-24</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1508,8 @@
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1504,7 +1521,8 @@
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Oman_Sovereign_Model.xlsx
+++ b/models/sovereigns/Oman_Sovereign_Model.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jun-25</t>
+          <t>01-Jun-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -774,7 +774,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dec-25</t>
+          <t>31-Dec-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>01-Jun-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -908,7 +908,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>01-Jun-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -964,7 +964,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Dec-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dec-24</t>
+          <t>31-Dec-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBO gross foreign assets and gold (OMR 7.068bn)</t>
+          <t>CBO gross foreign assets incl. gold (OMR 7.068bn)</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Dec-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dec-24</t>
+          <t>31-Dec-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27-Sep-24</t>
+          <t>27-Sep-24 (affirmed Sep-26)</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>National Centre for Statistics and Information, Jun-25</t>
+          <t>National Centre for Statistics and Information, 01-Jun-25</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       <c r="F5" s="2" t="n"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Central Bank of Oman / IMF, Jun-26</t>
+          <t>Central Bank of Oman / IMF, 01-Jun-26</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ministry of Finance / IMF, Jun-26</t>
+          <t>Ministry of Finance / IMF, 01-Jun-26 (2026F per IMF projection)</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ministry of Finance, Dec-25</t>
+          <t>Ministry of Finance, 31-Dec-25</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Central Bank of Oman, Dec-24</t>
+          <t>Central Bank of Oman, 31-Dec-24</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Oman_Sovereign_Model.xlsx
+++ b/models/sovereigns/Oman_Sovereign_Model.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01-Jun-25</t>
+          <t>Jun-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -774,12 +774,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31-Dec-25</t>
+          <t>Dec-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Central government debt</t>
+          <t>Central government debt (OMR 14.6bn / USD 37.9bn at end-2024 = 35.0% of GDP)</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance / IMF</t>
+          <t>Ministry of Finance / IMF (stated as ~0.6-0.7%)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -908,7 +908,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>01-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -974,12 +974,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>31-Dec-24</t>
+          <t>Dec-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBO gross foreign assets incl. gold (OMR 7.068bn)</t>
+          <t>CBO gross foreign assets and gold (OMR 7.068bn); excludes OIA assets of OMR 23bn / USD 59.7bn</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Central Bank of Oman</t>
+          <t>Central Bank of Oman (stated as over 5 months of merchandise imports)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>31-Dec-24</t>
+          <t>Dec-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27-Sep-24 (affirmed Sep-26)</t>
+          <t>27-Sep-24 (upgrade); affirmed Sep-26</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>National Centre for Statistics and Information, 01-Jun-25</t>
+          <t>National Centre for Statistics and Information, Jun-25</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       <c r="F5" s="2" t="n"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Central Bank of Oman / IMF, 01-Jun-26</t>
+          <t>Central Bank of Oman / IMF, Jun-26</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ministry of Finance / IMF, 01-Jun-26 (2026F per IMF projection)</t>
+          <t>Ministry of Finance / IMF, Jun-26 (2026F is IMF projection)</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ministry of Finance, 31-Dec-25</t>
+          <t>Ministry of Finance, Dec-25</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Central Bank of Oman, 31-Dec-24</t>
+          <t>Central Bank of Oman, Dec-24 (gross foreign assets and gold)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Oman_Sovereign_Model.xlsx
+++ b/models/sovereigns/Oman_Sovereign_Model.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Central government debt (OMR 14.6bn / USD 37.9bn at end-2024 = 35.0% of GDP)</t>
+          <t>Central government debt (approximate)</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance / IMF (stated as ~0.6-0.7%)</t>
+          <t>Ministry of Finance (stated ~0.6%-0.7%)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>Dec-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBO gross foreign assets and gold (OMR 7.068bn); excludes OIA assets of OMR 23bn / USD 59.7bn</t>
+          <t>CBO gross foreign assets and gold (OMR 7.068bn)</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27-Sep-24 (upgrade); affirmed Sep-26</t>
+          <t>27-Sep-24</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ministry of Finance / IMF, Jun-26 (2026F is IMF projection)</t>
+          <t>Ministry of Finance / IMF, Jun-26 (2026F is the IMF projection)</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Central Bank of Oman, Dec-24 (gross foreign assets and gold)</t>
+          <t>Central Bank of Oman, Dec-24</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Oman_Sovereign_Model.xlsx
+++ b/models/sovereigns/Oman_Sovereign_Model.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Central government debt (approximate)</t>
+          <t>Central government debt</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance (stated ~0.6%-0.7%)</t>
+          <t>Ministry of Finance</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBO gross foreign assets and gold (OMR 7.068bn)</t>
+          <t>CBO gross foreign assets and gold (OMR 7.068bn); excludes OIA assets</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27-Sep-24</t>
+          <t>Sep-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Oman_Sovereign_Model.xlsx
+++ b/models/sovereigns/Oman_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/oman.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/oman.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Oman_Sovereign_Model.xlsx
+++ b/models/sovereigns/Oman_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/oman.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/oman.json</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">

--- a/models/sovereigns/Oman_Sovereign_Model.xlsx
+++ b/models/sovereigns/Oman_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/oman.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/oman.json</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
